--- a/results/agreement_metrics/feature_human_agreement.xlsx
+++ b/results/agreement_metrics/feature_human_agreement.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="37">
   <si>
     <t>Feature-Based Methods vs. Human Annotations</t>
   </si>
   <si>
-    <t>correlation_weights vs. Human (IT) Method</t>
+    <t>S1_opt_correlation_en Method</t>
   </si>
   <si>
     <t>Overall Metrics</t>
@@ -58,49 +58,73 @@
     <t>Items</t>
   </si>
   <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>S1_opt_correlation_it Method</t>
+  </si>
+  <si>
     <t>it</t>
   </si>
   <si>
-    <t>uniform_weights vs. Human (IT) Method</t>
-  </si>
-  <si>
-    <t>literature_weights vs. Human (IT) Method</t>
-  </si>
-  <si>
-    <t>correlation_weights vs. Human (NB) Method</t>
+    <t>S1_opt_correlation_es Method</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>S1_opt_correlation_nb Method</t>
   </si>
   <si>
     <t>nb</t>
   </si>
   <si>
-    <t>uniform_weights vs. Human (NB) Method</t>
-  </si>
-  <si>
-    <t>literature_weights vs. Human (NB) Method</t>
-  </si>
-  <si>
-    <t>correlation_weights vs. Human (EN) Method</t>
-  </si>
-  <si>
-    <t>en</t>
-  </si>
-  <si>
-    <t>uniform_weights vs. Human (EN) Method</t>
-  </si>
-  <si>
-    <t>literature_weights vs. Human (EN) Method</t>
-  </si>
-  <si>
-    <t>correlation_weights vs. Human (ES) Method</t>
-  </si>
-  <si>
-    <t>es</t>
-  </si>
-  <si>
-    <t>uniform_weights vs. Human (ES) Method</t>
-  </si>
-  <si>
-    <t>literature_weights vs. Human (ES) Method</t>
+    <t>S2_opt_literature_en Method</t>
+  </si>
+  <si>
+    <t>S2_opt_literature_it Method</t>
+  </si>
+  <si>
+    <t>S2_opt_literature_es Method</t>
+  </si>
+  <si>
+    <t>S2_opt_literature_nb Method</t>
+  </si>
+  <si>
+    <t>S3_opt_uniform_en Method</t>
+  </si>
+  <si>
+    <t>S3_opt_uniform_it Method</t>
+  </si>
+  <si>
+    <t>S3_opt_uniform_es Method</t>
+  </si>
+  <si>
+    <t>S3_opt_uniform_nb Method</t>
+  </si>
+  <si>
+    <t>S4_nonopt_literature_en Method</t>
+  </si>
+  <si>
+    <t>S4_nonopt_literature_it Method</t>
+  </si>
+  <si>
+    <t>S4_nonopt_literature_es Method</t>
+  </si>
+  <si>
+    <t>S4_nonopt_literature_nb Method</t>
+  </si>
+  <si>
+    <t>S5_nonopt_uniform_en Method</t>
+  </si>
+  <si>
+    <t>S5_nonopt_uniform_it Method</t>
+  </si>
+  <si>
+    <t>S5_nonopt_uniform_es Method</t>
+  </si>
+  <si>
+    <t>S5_nonopt_uniform_nb Method</t>
   </si>
 </sst>
 </file>
@@ -484,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -511,7 +535,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2830188679245284</v>
+        <v>0.4133967499009117</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -519,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="5">
-        <v>0.5375</v>
+        <v>0.6125</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -527,7 +551,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="5">
-        <v>0.8375</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -535,7 +559,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="4">
-        <v>0.5</v>
+        <v>0.6125</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -576,16 +600,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="4">
-        <v>0.2830188679245284</v>
+        <v>0.4133967499009117</v>
       </c>
       <c r="C13" s="5">
-        <v>0.5375</v>
+        <v>0.6125</v>
       </c>
       <c r="D13" s="5">
-        <v>0.8375</v>
+        <v>0.775</v>
       </c>
       <c r="E13" s="4">
-        <v>0.5</v>
+        <v>0.6125</v>
       </c>
       <c r="F13" s="3">
         <v>80</v>
@@ -606,7 +630,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="4">
-        <v>0.2103639728562615</v>
+        <v>0.4479830148619958</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -614,7 +638,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="5">
-        <v>0.375</v>
+        <v>0.5375</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -622,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="5">
-        <v>0.6</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -630,7 +654,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="4">
-        <v>1.15</v>
+        <v>0.5375</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -668,19 +692,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B26" s="4">
-        <v>0.2103639728562615</v>
+        <v>0.4479830148619958</v>
       </c>
       <c r="C26" s="5">
-        <v>0.375</v>
+        <v>0.5375</v>
       </c>
       <c r="D26" s="5">
-        <v>0.6</v>
+        <v>0.7875</v>
       </c>
       <c r="E26" s="4">
-        <v>1.15</v>
+        <v>0.5375</v>
       </c>
       <c r="F26" s="3">
         <v>80</v>
@@ -688,7 +712,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -701,7 +725,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="4">
-        <v>0.2081911262798635</v>
+        <v>0.05691056910569103</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -709,7 +733,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="5">
-        <v>0.375</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -717,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="5">
-        <v>0.625</v>
+        <v>0.7375</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -725,7 +749,7 @@
         <v>6</v>
       </c>
       <c r="B34" s="4">
-        <v>0.925</v>
+        <v>1.5875</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -763,19 +787,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B39" s="4">
-        <v>0.2081911262798635</v>
+        <v>0.05691056910569103</v>
       </c>
       <c r="C39" s="5">
-        <v>0.375</v>
+        <v>0.15</v>
       </c>
       <c r="D39" s="5">
-        <v>0.625</v>
+        <v>0.7375</v>
       </c>
       <c r="E39" s="4">
-        <v>0.925</v>
+        <v>1.5875</v>
       </c>
       <c r="F39" s="3">
         <v>80</v>
@@ -783,7 +807,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -796,7 +820,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="4">
-        <v>0.2717584369449378</v>
+        <v>0.4233687405159333</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -804,7 +828,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="5">
-        <v>0.55</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -812,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="5">
-        <v>0.85</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -820,7 +844,7 @@
         <v>6</v>
       </c>
       <c r="B47" s="4">
-        <v>0.6375</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -858,19 +882,19 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B52" s="4">
-        <v>0.2717584369449378</v>
+        <v>0.4233687405159333</v>
       </c>
       <c r="C52" s="5">
-        <v>0.55</v>
+        <v>0.575</v>
       </c>
       <c r="D52" s="5">
-        <v>0.85</v>
+        <v>0.8875</v>
       </c>
       <c r="E52" s="4">
-        <v>0.6375</v>
+        <v>0.575</v>
       </c>
       <c r="F52" s="3">
         <v>80</v>
@@ -878,7 +902,7 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -891,7 +915,7 @@
         <v>3</v>
       </c>
       <c r="B57" s="4">
-        <v>0.2061281337047354</v>
+        <v>0.2928176795580111</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -899,7 +923,7 @@
         <v>4</v>
       </c>
       <c r="B58" s="5">
-        <v>0.4</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -907,7 +931,7 @@
         <v>5</v>
       </c>
       <c r="B59" s="5">
-        <v>0.725</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -915,7 +939,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="4">
-        <v>0.9375</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -953,19 +977,19 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B65" s="4">
-        <v>0.2061281337047354</v>
+        <v>0.2928176795580111</v>
       </c>
       <c r="C65" s="5">
-        <v>0.4</v>
+        <v>0.5125</v>
       </c>
       <c r="D65" s="5">
-        <v>0.725</v>
+        <v>0.6875</v>
       </c>
       <c r="E65" s="4">
-        <v>0.9375</v>
+        <v>0.85</v>
       </c>
       <c r="F65" s="3">
         <v>80</v>
@@ -973,7 +997,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -986,7 +1010,7 @@
         <v>3</v>
       </c>
       <c r="B70" s="4">
-        <v>0.3877551020408163</v>
+        <v>0.4472727272727273</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -994,7 +1018,7 @@
         <v>4</v>
       </c>
       <c r="B71" s="5">
-        <v>0.5375</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -1002,7 +1026,7 @@
         <v>5</v>
       </c>
       <c r="B72" s="5">
-        <v>0.85</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -1010,7 +1034,7 @@
         <v>6</v>
       </c>
       <c r="B73" s="4">
-        <v>0.5375</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -1048,19 +1072,19 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B78" s="4">
-        <v>0.3877551020408163</v>
+        <v>0.4472727272727273</v>
       </c>
       <c r="C78" s="5">
-        <v>0.5375</v>
+        <v>0.5625</v>
       </c>
       <c r="D78" s="5">
-        <v>0.85</v>
+        <v>0.7875</v>
       </c>
       <c r="E78" s="4">
-        <v>0.5375</v>
+        <v>0.55</v>
       </c>
       <c r="F78" s="3">
         <v>80</v>
@@ -1068,7 +1092,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -1081,7 +1105,7 @@
         <v>3</v>
       </c>
       <c r="B83" s="4">
-        <v>0.3973634651600754</v>
+        <v>0.08256880733944949</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -1089,7 +1113,7 @@
         <v>4</v>
       </c>
       <c r="B84" s="5">
-        <v>0.625</v>
+        <v>0.3875</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -1097,7 +1121,7 @@
         <v>5</v>
       </c>
       <c r="B85" s="5">
-        <v>0.85</v>
+        <v>0.7375</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -1105,7 +1129,7 @@
         <v>6</v>
       </c>
       <c r="B86" s="4">
-        <v>0.45</v>
+        <v>1.2125</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -1143,19 +1167,19 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B91" s="4">
-        <v>0.3973634651600754</v>
+        <v>0.08256880733944949</v>
       </c>
       <c r="C91" s="5">
-        <v>0.625</v>
+        <v>0.3875</v>
       </c>
       <c r="D91" s="5">
-        <v>0.85</v>
+        <v>0.7375</v>
       </c>
       <c r="E91" s="4">
-        <v>0.45</v>
+        <v>1.2125</v>
       </c>
       <c r="F91" s="3">
         <v>80</v>
@@ -1163,7 +1187,7 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -1176,7 +1200,7 @@
         <v>3</v>
       </c>
       <c r="B96" s="4">
-        <v>0.1137664924072692</v>
+        <v>0.5015576323987538</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -1184,7 +1208,7 @@
         <v>4</v>
       </c>
       <c r="B97" s="5">
-        <v>0.2</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -1192,7 +1216,7 @@
         <v>5</v>
       </c>
       <c r="B98" s="5">
-        <v>0.45</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -1200,7 +1224,7 @@
         <v>6</v>
       </c>
       <c r="B99" s="4">
-        <v>1.7625</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -1238,19 +1262,19 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B104" s="4">
-        <v>0.1137664924072692</v>
+        <v>0.5015576323987538</v>
       </c>
       <c r="C104" s="5">
-        <v>0.2</v>
+        <v>0.6375</v>
       </c>
       <c r="D104" s="5">
-        <v>0.45</v>
+        <v>0.8875</v>
       </c>
       <c r="E104" s="4">
-        <v>1.7625</v>
+        <v>0.475</v>
       </c>
       <c r="F104" s="3">
         <v>80</v>
@@ -1258,7 +1282,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -1271,7 +1295,7 @@
         <v>3</v>
       </c>
       <c r="B109" s="4">
-        <v>0.2633279483037156</v>
+        <v>0.3453573814295257</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -1279,7 +1303,7 @@
         <v>4</v>
       </c>
       <c r="B110" s="5">
-        <v>0.4125</v>
+        <v>0.5375</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -1287,7 +1311,7 @@
         <v>5</v>
       </c>
       <c r="B111" s="5">
-        <v>0.625</v>
+        <v>0.6625</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -1295,7 +1319,7 @@
         <v>6</v>
       </c>
       <c r="B112" s="4">
-        <v>0.9625</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -1333,19 +1357,19 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B117" s="4">
-        <v>0.2633279483037156</v>
+        <v>0.3453573814295257</v>
       </c>
       <c r="C117" s="5">
-        <v>0.4125</v>
+        <v>0.5375</v>
       </c>
       <c r="D117" s="5">
-        <v>0.625</v>
+        <v>0.6625</v>
       </c>
       <c r="E117" s="4">
-        <v>0.9625</v>
+        <v>0.9125</v>
       </c>
       <c r="F117" s="3">
         <v>80</v>
@@ -1353,7 +1377,7 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -1366,7 +1390,7 @@
         <v>3</v>
       </c>
       <c r="B122" s="4">
-        <v>0.05000000000000004</v>
+        <v>0.3515106853352984</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -1374,7 +1398,7 @@
         <v>4</v>
       </c>
       <c r="B123" s="5">
-        <v>0.2875</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -1382,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="B124" s="5">
-        <v>0.95</v>
+        <v>0.7625</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -1390,7 +1414,7 @@
         <v>6</v>
       </c>
       <c r="B125" s="4">
-        <v>0.7125</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -1428,19 +1452,19 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B130" s="4">
-        <v>0.05000000000000004</v>
+        <v>0.3515106853352984</v>
       </c>
       <c r="C130" s="5">
-        <v>0.2875</v>
+        <v>0.5</v>
       </c>
       <c r="D130" s="5">
-        <v>0.95</v>
+        <v>0.7625</v>
       </c>
       <c r="E130" s="4">
-        <v>0.7125</v>
+        <v>0.65</v>
       </c>
       <c r="F130" s="3">
         <v>80</v>
@@ -1461,7 +1485,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="4">
-        <v>0.02540608079966689</v>
+        <v>0.1370174110522331</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -1469,7 +1493,7 @@
         <v>4</v>
       </c>
       <c r="B136" s="5">
-        <v>0.08749999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -1477,7 +1501,7 @@
         <v>5</v>
       </c>
       <c r="B137" s="5">
-        <v>0.4125</v>
+        <v>0.7125</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -1485,7 +1509,7 @@
         <v>6</v>
       </c>
       <c r="B138" s="4">
-        <v>2.6125</v>
+        <v>1.1375</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -1523,19 +1547,19 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B143" s="4">
-        <v>0.02540608079966689</v>
+        <v>0.1370174110522331</v>
       </c>
       <c r="C143" s="5">
-        <v>0.08749999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="D143" s="5">
-        <v>0.4125</v>
+        <v>0.7125</v>
       </c>
       <c r="E143" s="4">
-        <v>2.6125</v>
+        <v>1.1375</v>
       </c>
       <c r="F143" s="3">
         <v>80</v>
@@ -1556,7 +1580,7 @@
         <v>3</v>
       </c>
       <c r="B148" s="4">
-        <v>0.03991370010787476</v>
+        <v>0.3114754098360656</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -1564,7 +1588,7 @@
         <v>4</v>
       </c>
       <c r="B149" s="5">
-        <v>0.2</v>
+        <v>0.5375</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -1572,7 +1596,7 @@
         <v>5</v>
       </c>
       <c r="B150" s="5">
-        <v>0.625</v>
+        <v>0.8375</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -1580,7 +1604,7 @@
         <v>6</v>
       </c>
       <c r="B151" s="4">
-        <v>1.7375</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -1618,21 +1642,781 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B156" s="4">
+        <v>0.3114754098360656</v>
+      </c>
+      <c r="C156" s="5">
+        <v>0.5375</v>
+      </c>
+      <c r="D156" s="5">
+        <v>0.8375</v>
+      </c>
+      <c r="E156" s="4">
+        <v>0.675</v>
+      </c>
+      <c r="F156" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B161" s="4">
+        <v>0.2633279483037156</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B162" s="5">
+        <v>0.4125</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B164" s="4">
+        <v>0.9625</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B165" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B169" s="4">
+        <v>0.2633279483037156</v>
+      </c>
+      <c r="C169" s="5">
+        <v>0.4125</v>
+      </c>
+      <c r="D169" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E169" s="4">
+        <v>0.9625</v>
+      </c>
+      <c r="F169" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B174" s="4">
+        <v>0.2081911262798635</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B175" s="5">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B176" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B177" s="4">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B178" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B182" s="4">
+        <v>0.2081911262798635</v>
+      </c>
+      <c r="C182" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="D182" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E182" s="4">
+        <v>0.925</v>
+      </c>
+      <c r="F182" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B187" s="4">
         <v>0.03991370010787476</v>
       </c>
-      <c r="C156" s="5">
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B188" s="5">
         <v>0.2</v>
       </c>
-      <c r="D156" s="5">
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B189" s="5">
         <v>0.625</v>
       </c>
-      <c r="E156" s="4">
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B190" s="4">
         <v>1.7375</v>
       </c>
-      <c r="F156" s="3">
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B191" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B195" s="4">
+        <v>0.03991370010787476</v>
+      </c>
+      <c r="C195" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D195" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E195" s="4">
+        <v>1.7375</v>
+      </c>
+      <c r="F195" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B200" s="4">
+        <v>0.3877551020408163</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B201" s="5">
+        <v>0.5375</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B202" s="5">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B203" s="4">
+        <v>0.5375</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B204" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B208" s="4">
+        <v>0.3877551020408163</v>
+      </c>
+      <c r="C208" s="5">
+        <v>0.5375</v>
+      </c>
+      <c r="D208" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="E208" s="4">
+        <v>0.5375</v>
+      </c>
+      <c r="F208" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B213" s="4">
+        <v>0.1137664924072692</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B214" s="5">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B215" s="5">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B216" s="4">
+        <v>1.7625</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B217" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B221" s="4">
+        <v>0.1137664924072692</v>
+      </c>
+      <c r="C221" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D221" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="E221" s="4">
+        <v>1.7625</v>
+      </c>
+      <c r="F221" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B226" s="4">
+        <v>0.2103639728562615</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B227" s="5">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B228" s="5">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B229" s="4">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B230" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B234" s="4">
+        <v>0.2103639728562615</v>
+      </c>
+      <c r="C234" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="D234" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="E234" s="4">
+        <v>1.15</v>
+      </c>
+      <c r="F234" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B239" s="4">
+        <v>0.02540608079966689</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B240" s="5">
+        <v>0.08749999999999999</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B241" s="5">
+        <v>0.4125</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B242" s="4">
+        <v>2.6125</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B243" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B247" s="4">
+        <v>0.02540608079966689</v>
+      </c>
+      <c r="C247" s="5">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="D247" s="5">
+        <v>0.4125</v>
+      </c>
+      <c r="E247" s="4">
+        <v>2.6125</v>
+      </c>
+      <c r="F247" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B252" s="4">
+        <v>0.2061281337047354</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B253" s="5">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B254" s="5">
+        <v>0.725</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B255" s="4">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B256" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B260" s="4">
+        <v>0.2061281337047354</v>
+      </c>
+      <c r="C260" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="D260" s="5">
+        <v>0.725</v>
+      </c>
+      <c r="E260" s="4">
+        <v>0.9375</v>
+      </c>
+      <c r="F260" s="3">
         <v>80</v>
       </c>
     </row>
